--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -2122,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118246995</v>
+        <v>118244912</v>
       </c>
       <c r="B16" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,38 +2134,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736671</v>
+        <v>736470</v>
       </c>
       <c r="R16" t="n">
-        <v>7371479</v>
+        <v>7371453</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,7 +2229,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118244912</v>
+        <v>118245007</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2258,21 +2263,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736470</v>
+        <v>736526</v>
       </c>
       <c r="R17" t="n">
-        <v>7371453</v>
+        <v>7371494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118245007</v>
+        <v>118246995</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736526</v>
+        <v>736671</v>
       </c>
       <c r="R18" t="n">
-        <v>7371494</v>
+        <v>7371479</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118244156</v>
+        <v>118243742</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736671</v>
+        <v>736742</v>
       </c>
       <c r="R22" t="n">
-        <v>7371425</v>
+        <v>7371361</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118245447</v>
+        <v>118245164</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,25 +2858,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736581</v>
+        <v>736560</v>
       </c>
       <c r="R23" t="n">
-        <v>7371502</v>
+        <v>7371508</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118243742</v>
+        <v>118245192</v>
       </c>
       <c r="B24" t="n">
         <v>90504</v>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736742</v>
+        <v>736533</v>
       </c>
       <c r="R24" t="n">
-        <v>7371361</v>
+        <v>7371534</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118245164</v>
+        <v>118244156</v>
       </c>
       <c r="B25" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,25 +3062,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736560</v>
+        <v>736671</v>
       </c>
       <c r="R25" t="n">
-        <v>7371508</v>
+        <v>7371425</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118245192</v>
+        <v>118245447</v>
       </c>
       <c r="B26" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,25 +3164,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736533</v>
+        <v>736581</v>
       </c>
       <c r="R26" t="n">
-        <v>7371534</v>
+        <v>7371502</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118244326</v>
+        <v>118245048</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>91196</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3985,25 +3985,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736625</v>
+        <v>736536</v>
       </c>
       <c r="R34" t="n">
-        <v>7371391</v>
+        <v>7371494</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118245048</v>
+        <v>118244227</v>
       </c>
       <c r="B35" t="n">
-        <v>91196</v>
+        <v>79565</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,25 +4087,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736536</v>
+        <v>736647</v>
       </c>
       <c r="R35" t="n">
-        <v>7371494</v>
+        <v>7371427</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4177,10 +4177,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118244227</v>
+        <v>118244326</v>
       </c>
       <c r="B36" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,25 +4189,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736647</v>
+        <v>736625</v>
       </c>
       <c r="R36" t="n">
-        <v>7371427</v>
+        <v>7371391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118243125</v>
+        <v>118243809</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4708,25 +4708,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736651</v>
+        <v>736744</v>
       </c>
       <c r="R41" t="n">
-        <v>7371348</v>
+        <v>7371373</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4772,6 +4772,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4798,10 +4803,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118243809</v>
+        <v>118243125</v>
       </c>
       <c r="B42" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,25 +4815,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4838,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736744</v>
+        <v>736651</v>
       </c>
       <c r="R42" t="n">
-        <v>7371373</v>
+        <v>7371348</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,11 +4879,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6236,10 +6236,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118244189</v>
+        <v>118245515</v>
       </c>
       <c r="B56" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6248,25 +6248,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736649</v>
+        <v>736572</v>
       </c>
       <c r="R56" t="n">
-        <v>7371433</v>
+        <v>7371491</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118245515</v>
+        <v>118244189</v>
       </c>
       <c r="B58" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6452,25 +6452,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736572</v>
+        <v>736649</v>
       </c>
       <c r="R58" t="n">
-        <v>7371491</v>
+        <v>7371433</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7378,10 +7378,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118242766</v>
+        <v>118246122</v>
       </c>
       <c r="B67" t="n">
-        <v>97846</v>
+        <v>79601</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7390,25 +7390,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736628</v>
+        <v>736843</v>
       </c>
       <c r="R67" t="n">
-        <v>7371390</v>
+        <v>7371612</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7480,10 +7480,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118246122</v>
+        <v>118242847</v>
       </c>
       <c r="B68" t="n">
-        <v>79601</v>
+        <v>79469</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7496,21 +7496,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736843</v>
+        <v>736630</v>
       </c>
       <c r="R68" t="n">
-        <v>7371612</v>
+        <v>7371386</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7582,10 +7582,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118242847</v>
+        <v>118244207</v>
       </c>
       <c r="B69" t="n">
-        <v>79469</v>
+        <v>79601</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7598,21 +7598,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7622,10 +7622,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736630</v>
+        <v>736653</v>
       </c>
       <c r="R69" t="n">
-        <v>7371386</v>
+        <v>7371419</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118244207</v>
+        <v>118242766</v>
       </c>
       <c r="B70" t="n">
-        <v>79601</v>
+        <v>97846</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7696,25 +7696,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736653</v>
+        <v>736628</v>
       </c>
       <c r="R70" t="n">
-        <v>7371419</v>
+        <v>7371390</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7888,10 +7888,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118243998</v>
+        <v>118245469</v>
       </c>
       <c r="B72" t="n">
-        <v>97846</v>
+        <v>91070</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7904,21 +7904,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>736682</v>
+        <v>736583</v>
       </c>
       <c r="R72" t="n">
-        <v>7371387</v>
+        <v>7371490</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7990,10 +7990,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118245469</v>
+        <v>118243316</v>
       </c>
       <c r="B73" t="n">
-        <v>91070</v>
+        <v>78555</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>760</v>
+        <v>639</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736583</v>
+        <v>736696</v>
       </c>
       <c r="R73" t="n">
-        <v>7371490</v>
+        <v>7371316</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8092,10 +8092,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118243316</v>
+        <v>118243998</v>
       </c>
       <c r="B74" t="n">
-        <v>78555</v>
+        <v>97846</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8108,21 +8108,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>639</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>736696</v>
+        <v>736682</v>
       </c>
       <c r="R74" t="n">
-        <v>7371316</v>
+        <v>7371387</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -2122,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118244912</v>
+        <v>118246995</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,43 +2134,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736470</v>
+        <v>736671</v>
       </c>
       <c r="R16" t="n">
-        <v>7371453</v>
+        <v>7371479</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,7 +2224,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118245007</v>
+        <v>118244912</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2263,16 +2258,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736526</v>
+        <v>736470</v>
       </c>
       <c r="R17" t="n">
-        <v>7371494</v>
+        <v>7371453</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118246995</v>
+        <v>118245007</v>
       </c>
       <c r="B18" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736671</v>
+        <v>736526</v>
       </c>
       <c r="R18" t="n">
-        <v>7371479</v>
+        <v>7371494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118245628</v>
+        <v>118244312</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736620</v>
+        <v>736637</v>
       </c>
       <c r="R19" t="n">
-        <v>7371551</v>
+        <v>7371397</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,6 +2509,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2535,7 +2540,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118244284</v>
+        <v>118245628</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736641</v>
+        <v>736620</v>
       </c>
       <c r="R20" t="n">
-        <v>7371403</v>
+        <v>7371551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118244312</v>
+        <v>118244284</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736637</v>
+        <v>736641</v>
       </c>
       <c r="R21" t="n">
-        <v>7371397</v>
+        <v>7371403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,11 +2718,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118243460</v>
+        <v>118246362</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4291,25 +4291,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736720</v>
+        <v>736858</v>
       </c>
       <c r="R37" t="n">
-        <v>7371362</v>
+        <v>7371606</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,10 +4381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118246362</v>
+        <v>118246887</v>
       </c>
       <c r="B38" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4397,34 +4397,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736858</v>
+        <v>736722</v>
       </c>
       <c r="R38" t="n">
-        <v>7371606</v>
+        <v>7371443</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,6 +4461,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4483,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118246887</v>
+        <v>118243460</v>
       </c>
       <c r="B39" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,42 +4504,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736722</v>
+        <v>736720</v>
       </c>
       <c r="R39" t="n">
-        <v>7371443</v>
+        <v>7371362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,11 +4568,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4696,10 +4696,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118243809</v>
+        <v>118243125</v>
       </c>
       <c r="B41" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4708,25 +4708,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736744</v>
+        <v>736651</v>
       </c>
       <c r="R41" t="n">
-        <v>7371373</v>
+        <v>7371348</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4772,11 +4772,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4803,10 +4798,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118243125</v>
+        <v>118243809</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4815,25 +4810,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4843,10 +4838,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736651</v>
+        <v>736744</v>
       </c>
       <c r="R42" t="n">
-        <v>7371348</v>
+        <v>7371373</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,6 +4874,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5420,10 +5420,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118245389</v>
+        <v>118243834</v>
       </c>
       <c r="B48" t="n">
-        <v>90788</v>
+        <v>5186</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5432,25 +5432,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5460,10 +5460,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736530</v>
+        <v>736743</v>
       </c>
       <c r="R48" t="n">
-        <v>7371527</v>
+        <v>7371379</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5522,10 +5522,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118243834</v>
+        <v>118245389</v>
       </c>
       <c r="B49" t="n">
-        <v>5186</v>
+        <v>90788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5534,25 +5534,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736743</v>
+        <v>736530</v>
       </c>
       <c r="R49" t="n">
-        <v>7371379</v>
+        <v>7371527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118242945</v>
+        <v>118245319</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5840,25 +5840,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736654</v>
+        <v>736512</v>
       </c>
       <c r="R52" t="n">
-        <v>7371344</v>
+        <v>7371520</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5930,10 +5930,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118245921</v>
+        <v>118244957</v>
       </c>
       <c r="B53" t="n">
-        <v>78566</v>
+        <v>97846</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5942,25 +5942,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736789</v>
+        <v>736478</v>
       </c>
       <c r="R53" t="n">
-        <v>7371715</v>
+        <v>7371508</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118244957</v>
+        <v>118242945</v>
       </c>
       <c r="B54" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6044,25 +6044,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736478</v>
+        <v>736654</v>
       </c>
       <c r="R54" t="n">
-        <v>7371508</v>
+        <v>7371344</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118245319</v>
+        <v>118245921</v>
       </c>
       <c r="B55" t="n">
-        <v>97846</v>
+        <v>78566</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6146,25 +6146,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736512</v>
+        <v>736789</v>
       </c>
       <c r="R55" t="n">
-        <v>7371520</v>
+        <v>7371715</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118245515</v>
+        <v>118244189</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6248,25 +6248,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736572</v>
+        <v>736649</v>
       </c>
       <c r="R56" t="n">
-        <v>7371491</v>
+        <v>7371433</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118244189</v>
+        <v>118245515</v>
       </c>
       <c r="B58" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6452,25 +6452,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736649</v>
+        <v>736572</v>
       </c>
       <c r="R58" t="n">
-        <v>7371433</v>
+        <v>7371491</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118243364</v>
+        <v>118246791</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>74596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736702</v>
+        <v>736766</v>
       </c>
       <c r="R2" t="n">
-        <v>7371313</v>
+        <v>7371440</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118246197</v>
+        <v>118245622</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736843</v>
+        <v>736620</v>
       </c>
       <c r="R3" t="n">
-        <v>7371612</v>
+        <v>7371551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118245797</v>
+        <v>118244326</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736563</v>
+        <v>736625</v>
       </c>
       <c r="R4" t="n">
-        <v>7371610</v>
+        <v>7371391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118243754</v>
+        <v>118243681</v>
       </c>
       <c r="B5" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736723</v>
+        <v>736703</v>
       </c>
       <c r="R5" t="n">
-        <v>7371369</v>
+        <v>7371374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118245334</v>
+        <v>118245137</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736512</v>
+        <v>736561</v>
       </c>
       <c r="R6" t="n">
-        <v>7371515</v>
+        <v>7371493</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118244968</v>
+        <v>118242766</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736499</v>
+        <v>736628</v>
       </c>
       <c r="R7" t="n">
-        <v>7371500</v>
+        <v>7371390</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118246827</v>
+        <v>118246232</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736739</v>
+        <v>736843</v>
       </c>
       <c r="R8" t="n">
-        <v>7371432</v>
+        <v>7371612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118243782</v>
+        <v>118244950</v>
       </c>
       <c r="B9" t="n">
-        <v>78566</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736718</v>
+        <v>736469</v>
       </c>
       <c r="R9" t="n">
-        <v>7371379</v>
+        <v>7371480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118247005</v>
+        <v>118245921</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>78566</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736660</v>
+        <v>736789</v>
       </c>
       <c r="R10" t="n">
-        <v>7371499</v>
+        <v>7371715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118242622</v>
+        <v>118246977</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>79565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,38 +1614,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkberg, Lu lm</t>
+          <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736588</v>
+        <v>736689</v>
       </c>
       <c r="R11" t="n">
-        <v>7371359</v>
+        <v>7371470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118245674</v>
+        <v>118243156</v>
       </c>
       <c r="B12" t="n">
-        <v>104925</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736594</v>
+        <v>736670</v>
       </c>
       <c r="R12" t="n">
-        <v>7371566</v>
+        <v>7371369</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118244245</v>
+        <v>118246980</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736644</v>
+        <v>736690</v>
       </c>
       <c r="R13" t="n">
-        <v>7371425</v>
+        <v>7371472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118244387</v>
+        <v>118246197</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736611</v>
+        <v>736843</v>
       </c>
       <c r="R14" t="n">
-        <v>7371375</v>
+        <v>7371612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118243156</v>
+        <v>118245764</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2060,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736670</v>
+        <v>736575</v>
       </c>
       <c r="R15" t="n">
-        <v>7371369</v>
+        <v>7371672</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118246995</v>
+        <v>118243037</v>
       </c>
       <c r="B16" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2162,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736671</v>
+        <v>736660</v>
       </c>
       <c r="R16" t="n">
-        <v>7371479</v>
+        <v>7371364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118244912</v>
+        <v>118244207</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>79601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,43 +2222,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736470</v>
+        <v>736653</v>
       </c>
       <c r="R17" t="n">
-        <v>7371453</v>
+        <v>7371419</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118245007</v>
+        <v>118245176</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2371,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736526</v>
+        <v>736558</v>
       </c>
       <c r="R18" t="n">
-        <v>7371494</v>
+        <v>7371508</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118244312</v>
+        <v>118242981</v>
       </c>
       <c r="B19" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736637</v>
+        <v>736676</v>
       </c>
       <c r="R19" t="n">
-        <v>7371397</v>
+        <v>7371333</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,7 +2494,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Skalad bark</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2540,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118245628</v>
+        <v>118245447</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2580,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736620</v>
+        <v>736581</v>
       </c>
       <c r="R20" t="n">
-        <v>7371551</v>
+        <v>7371502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118244284</v>
+        <v>118244845</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2682,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736641</v>
+        <v>736429</v>
       </c>
       <c r="R21" t="n">
-        <v>7371403</v>
+        <v>7371481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118243742</v>
+        <v>118245469</v>
       </c>
       <c r="B22" t="n">
-        <v>90504</v>
+        <v>91070</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736742</v>
+        <v>736583</v>
       </c>
       <c r="R22" t="n">
-        <v>7371361</v>
+        <v>7371490</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118245164</v>
+        <v>118245828</v>
       </c>
       <c r="B23" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736560</v>
+        <v>736601</v>
       </c>
       <c r="R23" t="n">
-        <v>7371508</v>
+        <v>7371631</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,6 +2903,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2948,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118245192</v>
+        <v>118246710</v>
       </c>
       <c r="B24" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,21 +2950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2988,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736533</v>
+        <v>736844</v>
       </c>
       <c r="R24" t="n">
-        <v>7371534</v>
+        <v>7371488</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118244156</v>
+        <v>118245334</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,25 +3048,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736671</v>
+        <v>736512</v>
       </c>
       <c r="R25" t="n">
-        <v>7371425</v>
+        <v>7371515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3126,6 +3112,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118245447</v>
+        <v>118243460</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3192,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736581</v>
+        <v>736720</v>
       </c>
       <c r="R26" t="n">
-        <v>7371502</v>
+        <v>7371362</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118246710</v>
+        <v>118245515</v>
       </c>
       <c r="B27" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,25 +3257,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736844</v>
+        <v>736572</v>
       </c>
       <c r="R27" t="n">
-        <v>7371488</v>
+        <v>7371491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118243479</v>
+        <v>118244797</v>
       </c>
       <c r="B28" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,25 +3359,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736715</v>
+        <v>736470</v>
       </c>
       <c r="R28" t="n">
-        <v>7371362</v>
+        <v>7371470</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118245828</v>
+        <v>118246995</v>
       </c>
       <c r="B29" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3474,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736601</v>
+        <v>736671</v>
       </c>
       <c r="R29" t="n">
-        <v>7371631</v>
+        <v>7371479</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3534,11 +3525,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3565,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118245176</v>
+        <v>118243667</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,25 +3563,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3605,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736558</v>
+        <v>736706</v>
       </c>
       <c r="R30" t="n">
-        <v>7371508</v>
+        <v>7371371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3641,6 +3627,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3667,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118243681</v>
+        <v>118245797</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3707,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736703</v>
+        <v>736563</v>
       </c>
       <c r="R31" t="n">
-        <v>7371374</v>
+        <v>7371610</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118246987</v>
+        <v>118245389</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,25 +3772,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3809,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736679</v>
+        <v>736530</v>
       </c>
       <c r="R32" t="n">
-        <v>7371476</v>
+        <v>7371527</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3871,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118244797</v>
+        <v>118245164</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3911,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736470</v>
+        <v>736560</v>
       </c>
       <c r="R33" t="n">
-        <v>7371470</v>
+        <v>7371508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118245048</v>
+        <v>118245674</v>
       </c>
       <c r="B34" t="n">
-        <v>91196</v>
+        <v>104925</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3989,21 +3980,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4013,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736536</v>
+        <v>736594</v>
       </c>
       <c r="R34" t="n">
-        <v>7371494</v>
+        <v>7371566</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4075,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118244227</v>
+        <v>118242945</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4091,21 +4082,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4115,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736647</v>
+        <v>736654</v>
       </c>
       <c r="R35" t="n">
-        <v>7371427</v>
+        <v>7371344</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4177,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118244326</v>
+        <v>118246771</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,25 +4180,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4217,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736625</v>
+        <v>736766</v>
       </c>
       <c r="R36" t="n">
-        <v>7371391</v>
+        <v>7371440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4253,6 +4244,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4279,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118246362</v>
+        <v>118244912</v>
       </c>
       <c r="B37" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4291,38 +4287,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736858</v>
+        <v>736470</v>
       </c>
       <c r="R37" t="n">
-        <v>7371606</v>
+        <v>7371453</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118246887</v>
+        <v>118242907</v>
       </c>
       <c r="B38" t="n">
-        <v>57290</v>
+        <v>97867</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,42 +4394,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736722</v>
+        <v>736631</v>
       </c>
       <c r="R38" t="n">
-        <v>7371443</v>
+        <v>7371360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4461,11 +4458,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4492,7 +4484,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118243460</v>
+        <v>118245007</v>
       </c>
       <c r="B39" t="n">
         <v>97846</v>
@@ -4532,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736720</v>
+        <v>736526</v>
       </c>
       <c r="R39" t="n">
-        <v>7371362</v>
+        <v>7371494</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,7 +4586,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118244845</v>
+        <v>118245069</v>
       </c>
       <c r="B40" t="n">
         <v>97846</v>
@@ -4634,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736429</v>
+        <v>736558</v>
       </c>
       <c r="R40" t="n">
-        <v>7371481</v>
+        <v>7371482</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4798,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118243809</v>
+        <v>118245319</v>
       </c>
       <c r="B42" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,25 +4802,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4838,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736744</v>
+        <v>736512</v>
       </c>
       <c r="R42" t="n">
-        <v>7371373</v>
+        <v>7371520</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,11 +4866,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4905,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118245391</v>
+        <v>118243364</v>
       </c>
       <c r="B43" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4917,25 +4904,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4945,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736530</v>
+        <v>736702</v>
       </c>
       <c r="R43" t="n">
-        <v>7371527</v>
+        <v>7371313</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5007,7 +4994,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118243874</v>
+        <v>118245096</v>
       </c>
       <c r="B44" t="n">
         <v>97846</v>
@@ -5047,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736715</v>
+        <v>736552</v>
       </c>
       <c r="R44" t="n">
-        <v>7371377</v>
+        <v>7371486</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5109,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118243667</v>
+        <v>118245192</v>
       </c>
       <c r="B45" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5125,21 +5112,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5149,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736706</v>
+        <v>736533</v>
       </c>
       <c r="R45" t="n">
-        <v>7371371</v>
+        <v>7371534</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5185,11 +5172,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5216,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118247000</v>
+        <v>118243782</v>
       </c>
       <c r="B46" t="n">
-        <v>79565</v>
+        <v>78566</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5232,21 +5214,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5256,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736668</v>
+        <v>736718</v>
       </c>
       <c r="R46" t="n">
-        <v>7371508</v>
+        <v>7371379</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5318,10 +5300,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118246791</v>
+        <v>118244387</v>
       </c>
       <c r="B47" t="n">
-        <v>74596</v>
+        <v>97846</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5330,25 +5312,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5358,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736766</v>
+        <v>736611</v>
       </c>
       <c r="R47" t="n">
-        <v>7371440</v>
+        <v>7371375</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5420,10 +5402,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118243834</v>
+        <v>118244968</v>
       </c>
       <c r="B48" t="n">
-        <v>5186</v>
+        <v>97846</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5432,25 +5414,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5460,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736743</v>
+        <v>736499</v>
       </c>
       <c r="R48" t="n">
-        <v>7371379</v>
+        <v>7371500</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5522,10 +5504,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118245389</v>
+        <v>118243874</v>
       </c>
       <c r="B49" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5534,25 +5516,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5562,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736530</v>
+        <v>736715</v>
       </c>
       <c r="R49" t="n">
-        <v>7371527</v>
+        <v>7371377</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5624,10 +5606,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118245137</v>
+        <v>118243754</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5636,25 +5618,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5664,10 +5646,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736561</v>
+        <v>736723</v>
       </c>
       <c r="R50" t="n">
-        <v>7371493</v>
+        <v>7371369</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5726,10 +5708,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118245096</v>
+        <v>118243742</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5738,25 +5720,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5766,10 +5748,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736552</v>
+        <v>736742</v>
       </c>
       <c r="R51" t="n">
-        <v>7371486</v>
+        <v>7371361</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,10 +5810,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118245319</v>
+        <v>118246362</v>
       </c>
       <c r="B52" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5840,25 +5822,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5868,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736512</v>
+        <v>736858</v>
       </c>
       <c r="R52" t="n">
-        <v>7371520</v>
+        <v>7371606</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5930,10 +5912,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118244957</v>
+        <v>118244783</v>
       </c>
       <c r="B53" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5942,25 +5924,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5970,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736478</v>
+        <v>736479</v>
       </c>
       <c r="R53" t="n">
-        <v>7371508</v>
+        <v>7371475</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,6 +5988,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6032,10 +6019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118242945</v>
+        <v>118247000</v>
       </c>
       <c r="B54" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6048,21 +6035,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6072,10 +6059,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736654</v>
+        <v>736668</v>
       </c>
       <c r="R54" t="n">
-        <v>7371344</v>
+        <v>7371508</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6134,10 +6121,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118245921</v>
+        <v>118242622</v>
       </c>
       <c r="B55" t="n">
-        <v>78566</v>
+        <v>57290</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6150,34 +6137,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björkberg (Björkberg), Lu lm</t>
+          <t>Björkberg, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736789</v>
+        <v>736588</v>
       </c>
       <c r="R55" t="n">
-        <v>7371715</v>
+        <v>7371359</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6210,6 +6201,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6236,10 +6232,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118244189</v>
+        <v>118246987</v>
       </c>
       <c r="B56" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6248,25 +6244,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6272,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736649</v>
+        <v>736679</v>
       </c>
       <c r="R56" t="n">
-        <v>7371433</v>
+        <v>7371476</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6338,10 +6334,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118246232</v>
+        <v>118243809</v>
       </c>
       <c r="B57" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6354,21 +6350,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6378,10 +6374,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736843</v>
+        <v>736744</v>
       </c>
       <c r="R57" t="n">
-        <v>7371612</v>
+        <v>7371373</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6414,6 +6410,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6440,10 +6441,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118245515</v>
+        <v>118242847</v>
       </c>
       <c r="B58" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6452,25 +6453,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6480,10 +6481,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736572</v>
+        <v>736630</v>
       </c>
       <c r="R58" t="n">
-        <v>7371491</v>
+        <v>7371386</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6542,10 +6543,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118246980</v>
+        <v>118243834</v>
       </c>
       <c r="B59" t="n">
-        <v>79469</v>
+        <v>5186</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6558,21 +6559,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6582,10 +6583,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736690</v>
+        <v>736743</v>
       </c>
       <c r="R59" t="n">
-        <v>7371472</v>
+        <v>7371379</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,10 +6645,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118244950</v>
+        <v>118244156</v>
       </c>
       <c r="B60" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6656,25 +6657,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6684,10 +6685,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736469</v>
+        <v>736671</v>
       </c>
       <c r="R60" t="n">
-        <v>7371480</v>
+        <v>7371425</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6720,11 +6721,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6751,10 +6747,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118242907</v>
+        <v>118246827</v>
       </c>
       <c r="B61" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6763,25 +6759,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6791,10 +6787,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736631</v>
+        <v>736739</v>
       </c>
       <c r="R61" t="n">
-        <v>7371360</v>
+        <v>7371432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,7 +6849,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118246771</v>
+        <v>118246887</v>
       </c>
       <c r="B62" t="n">
         <v>57290</v>
@@ -6887,16 +6883,20 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736766</v>
+        <v>736722</v>
       </c>
       <c r="R62" t="n">
-        <v>7371440</v>
+        <v>7371443</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6960,10 +6960,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118242981</v>
+        <v>118244227</v>
       </c>
       <c r="B63" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6972,25 +6972,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7000,10 +7000,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736676</v>
+        <v>736647</v>
       </c>
       <c r="R63" t="n">
-        <v>7371333</v>
+        <v>7371427</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7036,11 +7036,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7067,10 +7062,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118243037</v>
+        <v>118243316</v>
       </c>
       <c r="B64" t="n">
-        <v>97846</v>
+        <v>78555</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7083,21 +7078,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>639</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7107,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736660</v>
+        <v>736696</v>
       </c>
       <c r="R64" t="n">
-        <v>7371364</v>
+        <v>7371316</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7169,10 +7164,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118245069</v>
+        <v>118243479</v>
       </c>
       <c r="B65" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7181,25 +7176,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7209,10 +7204,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736558</v>
+        <v>736715</v>
       </c>
       <c r="R65" t="n">
-        <v>7371482</v>
+        <v>7371362</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7271,10 +7266,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118244783</v>
+        <v>118244245</v>
       </c>
       <c r="B66" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7283,25 +7278,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7311,10 +7306,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>736479</v>
+        <v>736644</v>
       </c>
       <c r="R66" t="n">
-        <v>7371475</v>
+        <v>7371425</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7347,11 +7342,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7378,10 +7368,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118246122</v>
+        <v>118245391</v>
       </c>
       <c r="B67" t="n">
-        <v>79601</v>
+        <v>90504</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7390,25 +7380,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7418,10 +7408,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736843</v>
+        <v>736530</v>
       </c>
       <c r="R67" t="n">
-        <v>7371612</v>
+        <v>7371527</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7480,10 +7470,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118242847</v>
+        <v>118245628</v>
       </c>
       <c r="B68" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7492,25 +7482,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7520,10 +7510,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736630</v>
+        <v>736620</v>
       </c>
       <c r="R68" t="n">
-        <v>7371386</v>
+        <v>7371551</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7582,10 +7572,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118244207</v>
+        <v>118245397</v>
       </c>
       <c r="B69" t="n">
-        <v>79601</v>
+        <v>97846</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7594,25 +7584,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7622,10 +7612,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736653</v>
+        <v>736534</v>
       </c>
       <c r="R69" t="n">
-        <v>7371419</v>
+        <v>7371536</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7684,7 +7674,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118242766</v>
+        <v>118243998</v>
       </c>
       <c r="B70" t="n">
         <v>97846</v>
@@ -7724,10 +7714,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736628</v>
+        <v>736682</v>
       </c>
       <c r="R70" t="n">
-        <v>7371390</v>
+        <v>7371387</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7786,10 +7776,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118245764</v>
+        <v>118244957</v>
       </c>
       <c r="B71" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7798,25 +7788,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7826,10 +7816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736575</v>
+        <v>736478</v>
       </c>
       <c r="R71" t="n">
-        <v>7371672</v>
+        <v>7371508</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7888,10 +7878,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118245469</v>
+        <v>118246122</v>
       </c>
       <c r="B72" t="n">
-        <v>91070</v>
+        <v>79601</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7900,25 +7890,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7928,10 +7918,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>736583</v>
+        <v>736843</v>
       </c>
       <c r="R72" t="n">
-        <v>7371490</v>
+        <v>7371612</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7990,10 +7980,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118243316</v>
+        <v>118244189</v>
       </c>
       <c r="B73" t="n">
-        <v>78555</v>
+        <v>79469</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8002,25 +7992,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>639</v>
+        <v>6456</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8030,10 +8020,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736696</v>
+        <v>736649</v>
       </c>
       <c r="R73" t="n">
-        <v>7371316</v>
+        <v>7371433</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8092,10 +8082,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118243998</v>
+        <v>118245048</v>
       </c>
       <c r="B74" t="n">
-        <v>97846</v>
+        <v>91196</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8104,25 +8094,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8132,10 +8122,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>736682</v>
+        <v>736536</v>
       </c>
       <c r="R74" t="n">
-        <v>7371387</v>
+        <v>7371494</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8194,10 +8184,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118245397</v>
+        <v>118247005</v>
       </c>
       <c r="B75" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8206,25 +8196,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8234,10 +8224,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736534</v>
+        <v>736660</v>
       </c>
       <c r="R75" t="n">
-        <v>7371536</v>
+        <v>7371499</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8270,6 +8260,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8296,10 +8291,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118246977</v>
+        <v>118244312</v>
       </c>
       <c r="B76" t="n">
-        <v>79565</v>
+        <v>57290</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8312,21 +8307,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8336,10 +8331,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736689</v>
+        <v>736637</v>
       </c>
       <c r="R76" t="n">
-        <v>7371470</v>
+        <v>7371397</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8372,6 +8367,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8398,10 +8398,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118245622</v>
+        <v>118244284</v>
       </c>
       <c r="B77" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8410,25 +8410,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8438,10 +8438,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736620</v>
+        <v>736641</v>
       </c>
       <c r="R77" t="n">
-        <v>7371551</v>
+        <v>7371403</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118246771</v>
+        <v>118244912</v>
       </c>
       <c r="B36" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4180,38 +4180,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736766</v>
+        <v>736470</v>
       </c>
       <c r="R36" t="n">
-        <v>7371440</v>
+        <v>7371453</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,11 +4249,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118244912</v>
+        <v>118246771</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4287,43 +4287,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Björkberg (Björkberg), Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736470</v>
+        <v>736766</v>
       </c>
       <c r="R37" t="n">
-        <v>7371453</v>
+        <v>7371440</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,6 +4351,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -7470,10 +7470,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118245628</v>
+        <v>118246122</v>
       </c>
       <c r="B68" t="n">
-        <v>97846</v>
+        <v>79601</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7482,25 +7482,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736620</v>
+        <v>736843</v>
       </c>
       <c r="R68" t="n">
-        <v>7371551</v>
+        <v>7371612</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7572,10 +7572,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118245397</v>
+        <v>118244189</v>
       </c>
       <c r="B69" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7584,25 +7584,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736534</v>
+        <v>736649</v>
       </c>
       <c r="R69" t="n">
-        <v>7371536</v>
+        <v>7371433</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7674,7 +7674,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118243998</v>
+        <v>118245628</v>
       </c>
       <c r="B70" t="n">
         <v>97846</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736682</v>
+        <v>736620</v>
       </c>
       <c r="R70" t="n">
-        <v>7371387</v>
+        <v>7371551</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7776,7 +7776,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118244957</v>
+        <v>118245397</v>
       </c>
       <c r="B71" t="n">
         <v>97846</v>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736478</v>
+        <v>736534</v>
       </c>
       <c r="R71" t="n">
-        <v>7371508</v>
+        <v>7371536</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7878,10 +7878,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118246122</v>
+        <v>118243998</v>
       </c>
       <c r="B72" t="n">
-        <v>79601</v>
+        <v>97846</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7890,25 +7890,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>736843</v>
+        <v>736682</v>
       </c>
       <c r="R72" t="n">
-        <v>7371612</v>
+        <v>7371387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7980,10 +7980,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118244189</v>
+        <v>118244957</v>
       </c>
       <c r="B73" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7992,25 +7992,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8020,10 +8020,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736649</v>
+        <v>736478</v>
       </c>
       <c r="R73" t="n">
-        <v>7371433</v>
+        <v>7371508</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8498,6 +8498,108 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122440322</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Björkberg, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>736900</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7371711</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Isabelle Holmström</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Isabelle Holmström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8503,7 +8503,7 @@
         <v>122440322</v>
       </c>
       <c r="B78" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8503,7 +8503,7 @@
         <v>122440322</v>
       </c>
       <c r="B78" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8517,11 +8517,6 @@
       </c>
       <c r="E78" t="n">
         <v>6425</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8503,7 +8503,7 @@
         <v>122440322</v>
       </c>
       <c r="B78" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8517,6 +8517,11 @@
       </c>
       <c r="E78" t="n">
         <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8503,7 +8503,7 @@
         <v>122440322</v>
       </c>
       <c r="B78" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8503,7 +8503,7 @@
         <v>122440322</v>
       </c>
       <c r="B78" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8503,7 +8503,7 @@
         <v>122440322</v>
       </c>
       <c r="B78" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +8600,1282 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125981813</v>
+      </c>
+      <c r="B79" t="n">
+        <v>82779</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>737058</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7371922</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125981796</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>658</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>736749</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7371803</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125981799</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>737011</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7371930</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125981795</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>737047</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7371926</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125981790</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80106</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>737051</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7371920</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125981785</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>736974</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7371943</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125981794</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>736742</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7371803</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125981802</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>736630</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7371739</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125981809</v>
+      </c>
+      <c r="B87" t="n">
+        <v>82779</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>737023</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7372056</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125981784</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>736748</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7371807</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Under hela lågan</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125981800</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>736547</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7371492</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125981801</v>
+      </c>
+      <c r="B90" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>736972</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7371941</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125981786</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>737026</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7371930</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Avskalad granar</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8602,10 +8602,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125981813</v>
+        <v>125981808</v>
       </c>
       <c r="B79" t="n">
-        <v>82779</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8613,21 +8613,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>737058</v>
+        <v>736592</v>
       </c>
       <c r="R79" t="n">
-        <v>7371922</v>
+        <v>7371671</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8699,10 +8699,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125981796</v>
+        <v>125981813</v>
       </c>
       <c r="B80" t="n">
-        <v>91520</v>
+        <v>82780</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8710,21 +8710,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736749</v>
+        <v>737058</v>
       </c>
       <c r="R80" t="n">
-        <v>7371803</v>
+        <v>7371922</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981799</v>
+        <v>125981795</v>
       </c>
       <c r="B81" t="n">
-        <v>91245</v>
+        <v>80072</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>737011</v>
+        <v>737047</v>
       </c>
       <c r="R81" t="n">
-        <v>7371930</v>
+        <v>7371926</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981795</v>
+        <v>125981796</v>
       </c>
       <c r="B82" t="n">
-        <v>80071</v>
+        <v>91521</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>737047</v>
+        <v>736749</v>
       </c>
       <c r="R82" t="n">
-        <v>7371926</v>
+        <v>7371803</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8990,32 +8990,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981790</v>
+        <v>125981799</v>
       </c>
       <c r="B83" t="n">
-        <v>80106</v>
+        <v>91246</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>737051</v>
+        <v>737011</v>
       </c>
       <c r="R83" t="n">
-        <v>7371920</v>
+        <v>7371930</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9087,32 +9087,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125981785</v>
+        <v>125981790</v>
       </c>
       <c r="B84" t="n">
-        <v>57651</v>
+        <v>80107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9122,10 +9122,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736974</v>
+        <v>737051</v>
       </c>
       <c r="R84" t="n">
-        <v>7371943</v>
+        <v>7371920</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9152,17 +9152,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>avskalad gran</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9286,10 +9281,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125981802</v>
+        <v>125981785</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9297,21 +9292,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9321,10 +9316,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736630</v>
+        <v>736974</v>
       </c>
       <c r="R86" t="n">
-        <v>7371739</v>
+        <v>7371943</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9351,12 +9346,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9383,10 +9383,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125981809</v>
+        <v>125981802</v>
       </c>
       <c r="B87" t="n">
-        <v>82779</v>
+        <v>78968</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>737023</v>
+        <v>736630</v>
       </c>
       <c r="R87" t="n">
-        <v>7372056</v>
+        <v>7371739</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9480,10 +9480,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125981784</v>
+        <v>125981809</v>
       </c>
       <c r="B88" t="n">
-        <v>91227</v>
+        <v>82780</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9491,21 +9491,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736748</v>
+        <v>737023</v>
       </c>
       <c r="R88" t="n">
-        <v>7371807</v>
+        <v>7372056</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9551,11 +9551,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Under hela lågan</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9582,10 +9577,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125981800</v>
+        <v>125981784</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>91228</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9593,21 +9588,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9617,10 +9612,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736547</v>
+        <v>736748</v>
       </c>
       <c r="R89" t="n">
-        <v>7371492</v>
+        <v>7371807</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9647,12 +9642,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Under hela lågan</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9679,10 +9679,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125981801</v>
+        <v>125981800</v>
       </c>
       <c r="B90" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736972</v>
+        <v>736547</v>
       </c>
       <c r="R90" t="n">
-        <v>7371941</v>
+        <v>7371492</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9876,6 +9876,103 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125981801</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>736972</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7371941</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981795</v>
+        <v>125981796</v>
       </c>
       <c r="B81" t="n">
-        <v>80072</v>
+        <v>91524</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>737047</v>
+        <v>736749</v>
       </c>
       <c r="R81" t="n">
-        <v>7371926</v>
+        <v>7371803</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981796</v>
+        <v>125981795</v>
       </c>
       <c r="B82" t="n">
-        <v>91521</v>
+        <v>80072</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736749</v>
+        <v>737047</v>
       </c>
       <c r="R82" t="n">
-        <v>7371803</v>
+        <v>7371926</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8605,7 +8605,7 @@
         <v>125981808</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>125981813</v>
       </c>
       <c r="B80" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981796</v>
+        <v>125981799</v>
       </c>
       <c r="B81" t="n">
-        <v>91524</v>
+        <v>91250</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736749</v>
+        <v>737011</v>
       </c>
       <c r="R81" t="n">
-        <v>7371803</v>
+        <v>7371930</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8896,7 +8896,7 @@
         <v>125981795</v>
       </c>
       <c r="B82" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981799</v>
+        <v>125981796</v>
       </c>
       <c r="B83" t="n">
-        <v>91246</v>
+        <v>91528</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +9001,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>737011</v>
+        <v>736749</v>
       </c>
       <c r="R83" t="n">
-        <v>7371930</v>
+        <v>7371803</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9090,7 +9090,7 @@
         <v>125981790</v>
       </c>
       <c r="B84" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,10 +9184,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125981794</v>
+        <v>125981785</v>
       </c>
       <c r="B85" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9195,16 +9195,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736742</v>
+        <v>736974</v>
       </c>
       <c r="R85" t="n">
-        <v>7371803</v>
+        <v>7371943</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9249,12 +9249,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9281,10 +9286,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125981785</v>
+        <v>125981794</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9292,16 +9297,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9316,10 +9321,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736974</v>
+        <v>736742</v>
       </c>
       <c r="R86" t="n">
-        <v>7371943</v>
+        <v>7371803</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9346,17 +9351,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>avskalad gran</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9386,7 +9386,7 @@
         <v>125981802</v>
       </c>
       <c r="B87" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>125981809</v>
       </c>
       <c r="B88" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>125981784</v>
       </c>
       <c r="B89" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>125981800</v>
       </c>
       <c r="B90" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>125981801</v>
       </c>
       <c r="B92" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -9184,10 +9184,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125981785</v>
+        <v>125981794</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9195,16 +9195,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736974</v>
+        <v>736742</v>
       </c>
       <c r="R85" t="n">
-        <v>7371943</v>
+        <v>7371803</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9249,17 +9249,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>avskalad gran</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9286,10 +9281,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125981794</v>
+        <v>125981785</v>
       </c>
       <c r="B86" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9297,16 +9292,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9321,10 +9316,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736742</v>
+        <v>736974</v>
       </c>
       <c r="R86" t="n">
-        <v>7371803</v>
+        <v>7371943</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9351,12 +9346,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -9184,10 +9184,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125981794</v>
+        <v>125981785</v>
       </c>
       <c r="B85" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9195,16 +9195,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736742</v>
+        <v>736974</v>
       </c>
       <c r="R85" t="n">
-        <v>7371803</v>
+        <v>7371943</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9249,12 +9249,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9281,10 +9286,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125981785</v>
+        <v>125981794</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9292,16 +9297,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9316,10 +9321,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736974</v>
+        <v>736742</v>
       </c>
       <c r="R86" t="n">
-        <v>7371943</v>
+        <v>7371803</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9346,17 +9351,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>avskalad gran</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8605,7 +8605,7 @@
         <v>125981808</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>125981813</v>
       </c>
       <c r="B80" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>125981799</v>
       </c>
       <c r="B81" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>125981795</v>
       </c>
       <c r="B82" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>125981796</v>
       </c>
       <c r="B83" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>125981790</v>
       </c>
       <c r="B84" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,10 +9184,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125981785</v>
+        <v>125981794</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>57649</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9195,16 +9195,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736974</v>
+        <v>736742</v>
       </c>
       <c r="R85" t="n">
-        <v>7371943</v>
+        <v>7371803</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9249,17 +9249,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>avskalad gran</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9286,10 +9281,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125981794</v>
+        <v>125981785</v>
       </c>
       <c r="B86" t="n">
-        <v>57648</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9297,16 +9292,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9321,10 +9316,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736742</v>
+        <v>736974</v>
       </c>
       <c r="R86" t="n">
-        <v>7371803</v>
+        <v>7371943</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9351,12 +9346,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9386,7 +9386,7 @@
         <v>125981802</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>125981809</v>
       </c>
       <c r="B88" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>125981784</v>
       </c>
       <c r="B89" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>125981800</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>125981786</v>
       </c>
       <c r="B91" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>125981801</v>
       </c>
       <c r="B92" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>125981799</v>
       </c>
       <c r="B81" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>125981796</v>
       </c>
       <c r="B83" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>125981784</v>
       </c>
       <c r="B89" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125981786</v>
+        <v>125981801</v>
       </c>
       <c r="B91" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9787,21 +9787,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>737026</v>
+        <v>736972</v>
       </c>
       <c r="R91" t="n">
-        <v>7371930</v>
+        <v>7371941</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9841,17 +9841,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Avskalad granar</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9878,10 +9873,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125981801</v>
+        <v>125981786</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9889,21 +9884,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9913,10 +9908,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736972</v>
+        <v>737026</v>
       </c>
       <c r="R92" t="n">
-        <v>7371941</v>
+        <v>7371930</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9943,12 +9938,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Avskalad granar</t>
         </is>
       </c>
       <c r="AD92" t="b">

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981799</v>
+        <v>125981796</v>
       </c>
       <c r="B81" t="n">
-        <v>91254</v>
+        <v>91532</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>737011</v>
+        <v>736749</v>
       </c>
       <c r="R81" t="n">
-        <v>7371930</v>
+        <v>7371803</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981795</v>
+        <v>125981799</v>
       </c>
       <c r="B82" t="n">
-        <v>80077</v>
+        <v>91254</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>737047</v>
+        <v>737011</v>
       </c>
       <c r="R82" t="n">
-        <v>7371926</v>
+        <v>7371930</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981796</v>
+        <v>125981795</v>
       </c>
       <c r="B83" t="n">
-        <v>91532</v>
+        <v>80077</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +9001,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736749</v>
+        <v>737047</v>
       </c>
       <c r="R83" t="n">
-        <v>7371803</v>
+        <v>7371926</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9184,10 +9184,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125981794</v>
+        <v>125981785</v>
       </c>
       <c r="B85" t="n">
-        <v>57649</v>
+        <v>57652</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9195,16 +9195,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736742</v>
+        <v>736974</v>
       </c>
       <c r="R85" t="n">
-        <v>7371803</v>
+        <v>7371943</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9249,12 +9249,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9281,10 +9286,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125981785</v>
+        <v>125981794</v>
       </c>
       <c r="B86" t="n">
-        <v>57652</v>
+        <v>57649</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9292,16 +9297,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9316,10 +9321,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736974</v>
+        <v>736742</v>
       </c>
       <c r="R86" t="n">
-        <v>7371943</v>
+        <v>7371803</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9346,17 +9351,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>avskalad gran</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9776,10 +9776,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125981801</v>
+        <v>125981786</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9787,21 +9787,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736972</v>
+        <v>737026</v>
       </c>
       <c r="R91" t="n">
-        <v>7371941</v>
+        <v>7371930</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9841,12 +9841,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Avskalad granar</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9873,10 +9878,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125981786</v>
+        <v>125981801</v>
       </c>
       <c r="B92" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9884,21 +9889,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9908,10 +9913,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>737026</v>
+        <v>736972</v>
       </c>
       <c r="R92" t="n">
-        <v>7371930</v>
+        <v>7371941</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9938,17 +9943,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Avskalad granar</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD92" t="b">

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>125981796</v>
       </c>
       <c r="B81" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>125981799</v>
       </c>
       <c r="B82" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9184,10 +9184,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125981785</v>
+        <v>125981794</v>
       </c>
       <c r="B85" t="n">
-        <v>57652</v>
+        <v>57649</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9195,16 +9195,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736974</v>
+        <v>736742</v>
       </c>
       <c r="R85" t="n">
-        <v>7371943</v>
+        <v>7371803</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9249,17 +9249,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>avskalad gran</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9286,10 +9281,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125981794</v>
+        <v>125981785</v>
       </c>
       <c r="B86" t="n">
-        <v>57649</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9297,16 +9292,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9321,10 +9316,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736742</v>
+        <v>736974</v>
       </c>
       <c r="R86" t="n">
-        <v>7371803</v>
+        <v>7371943</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9351,12 +9346,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>avskalad gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9580,7 +9580,7 @@
         <v>125981784</v>
       </c>
       <c r="B89" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125981786</v>
+        <v>125981801</v>
       </c>
       <c r="B91" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9787,21 +9787,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>737026</v>
+        <v>736972</v>
       </c>
       <c r="R91" t="n">
-        <v>7371930</v>
+        <v>7371941</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9841,17 +9841,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Avskalad granar</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9878,10 +9873,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125981801</v>
+        <v>125981786</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9889,21 +9884,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9913,10 +9908,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736972</v>
+        <v>737026</v>
       </c>
       <c r="R92" t="n">
-        <v>7371941</v>
+        <v>7371930</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9943,12 +9938,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Avskalad granar</t>
         </is>
       </c>
       <c r="AD92" t="b">

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981796</v>
+        <v>125981799</v>
       </c>
       <c r="B81" t="n">
-        <v>91534</v>
+        <v>91256</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736749</v>
+        <v>737011</v>
       </c>
       <c r="R81" t="n">
-        <v>7371803</v>
+        <v>7371930</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981799</v>
+        <v>125981795</v>
       </c>
       <c r="B82" t="n">
-        <v>91256</v>
+        <v>80077</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>737011</v>
+        <v>737047</v>
       </c>
       <c r="R82" t="n">
-        <v>7371930</v>
+        <v>7371926</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981795</v>
+        <v>125981796</v>
       </c>
       <c r="B83" t="n">
-        <v>80077</v>
+        <v>91534</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +9001,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>737047</v>
+        <v>736749</v>
       </c>
       <c r="R83" t="n">
-        <v>7371926</v>
+        <v>7371803</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8605,7 +8605,7 @@
         <v>125981808</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>125981813</v>
       </c>
       <c r="B80" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981799</v>
+        <v>125981795</v>
       </c>
       <c r="B81" t="n">
-        <v>91256</v>
+        <v>80081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>737011</v>
+        <v>737047</v>
       </c>
       <c r="R81" t="n">
-        <v>7371930</v>
+        <v>7371926</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981795</v>
+        <v>125981796</v>
       </c>
       <c r="B82" t="n">
-        <v>80077</v>
+        <v>91538</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>737047</v>
+        <v>736749</v>
       </c>
       <c r="R82" t="n">
-        <v>7371926</v>
+        <v>7371803</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981796</v>
+        <v>125981799</v>
       </c>
       <c r="B83" t="n">
-        <v>91534</v>
+        <v>91260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +9001,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736749</v>
+        <v>737011</v>
       </c>
       <c r="R83" t="n">
-        <v>7371803</v>
+        <v>7371930</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9090,7 +9090,7 @@
         <v>125981790</v>
       </c>
       <c r="B84" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>125981794</v>
       </c>
       <c r="B85" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>125981785</v>
       </c>
       <c r="B86" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>125981802</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>125981809</v>
       </c>
       <c r="B88" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>125981784</v>
       </c>
       <c r="B89" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>125981800</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>125981801</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>125981786</v>
       </c>
       <c r="B92" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981795</v>
+        <v>125981799</v>
       </c>
       <c r="B81" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>737047</v>
+        <v>737011</v>
       </c>
       <c r="R81" t="n">
-        <v>7371926</v>
+        <v>7371930</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981796</v>
+        <v>125981795</v>
       </c>
       <c r="B82" t="n">
-        <v>91538</v>
+        <v>80081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736749</v>
+        <v>737047</v>
       </c>
       <c r="R82" t="n">
-        <v>7371803</v>
+        <v>7371926</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981799</v>
+        <v>125981796</v>
       </c>
       <c r="B83" t="n">
-        <v>91260</v>
+        <v>91538</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +9001,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>737011</v>
+        <v>736749</v>
       </c>
       <c r="R83" t="n">
-        <v>7371930</v>
+        <v>7371803</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981799</v>
+        <v>125981796</v>
       </c>
       <c r="B81" t="n">
-        <v>91260</v>
+        <v>91538</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>737011</v>
+        <v>736749</v>
       </c>
       <c r="R81" t="n">
-        <v>7371930</v>
+        <v>7371803</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981795</v>
+        <v>125981799</v>
       </c>
       <c r="B82" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>737047</v>
+        <v>737011</v>
       </c>
       <c r="R82" t="n">
-        <v>7371926</v>
+        <v>7371930</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981796</v>
+        <v>125981795</v>
       </c>
       <c r="B83" t="n">
-        <v>91538</v>
+        <v>80081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +9001,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736749</v>
+        <v>737047</v>
       </c>
       <c r="R83" t="n">
-        <v>7371803</v>
+        <v>7371926</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8796,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125981796</v>
+        <v>125981799</v>
       </c>
       <c r="B81" t="n">
-        <v>91538</v>
+        <v>91260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736749</v>
+        <v>737011</v>
       </c>
       <c r="R81" t="n">
-        <v>7371803</v>
+        <v>7371930</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125981799</v>
+        <v>125981795</v>
       </c>
       <c r="B82" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>737011</v>
+        <v>737047</v>
       </c>
       <c r="R82" t="n">
-        <v>7371930</v>
+        <v>7371926</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125981795</v>
+        <v>125981796</v>
       </c>
       <c r="B83" t="n">
-        <v>80081</v>
+        <v>91538</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +9001,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>737047</v>
+        <v>736749</v>
       </c>
       <c r="R83" t="n">
-        <v>7371926</v>
+        <v>7371803</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -8605,7 +8605,7 @@
         <v>125981808</v>
       </c>
       <c r="B79" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>125981813</v>
       </c>
       <c r="B80" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>125981799</v>
       </c>
       <c r="B81" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>125981795</v>
       </c>
       <c r="B82" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>125981796</v>
       </c>
       <c r="B83" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>125981790</v>
       </c>
       <c r="B84" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>125981794</v>
       </c>
       <c r="B85" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>125981785</v>
       </c>
       <c r="B86" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>125981802</v>
       </c>
       <c r="B87" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>125981809</v>
       </c>
       <c r="B88" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>125981784</v>
       </c>
       <c r="B89" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>125981800</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125981801</v>
+        <v>125981786</v>
       </c>
       <c r="B91" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9787,21 +9787,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736972</v>
+        <v>737026</v>
       </c>
       <c r="R91" t="n">
-        <v>7371941</v>
+        <v>7371930</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9841,12 +9841,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Avskalad granar</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9873,10 +9878,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125981786</v>
+        <v>125981801</v>
       </c>
       <c r="B92" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9884,21 +9889,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9908,10 +9913,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>737026</v>
+        <v>736972</v>
       </c>
       <c r="R92" t="n">
-        <v>7371930</v>
+        <v>7371941</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9938,17 +9943,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Avskalad granar</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD92" t="b">

--- a/artfynd/A 27667-2024 artfynd.xlsx
+++ b/artfynd/A 27667-2024 artfynd.xlsx
@@ -9776,10 +9776,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125981786</v>
+        <v>125981801</v>
       </c>
       <c r="B91" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9787,21 +9787,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>737026</v>
+        <v>736972</v>
       </c>
       <c r="R91" t="n">
-        <v>7371930</v>
+        <v>7371941</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9841,17 +9841,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Avskalad granar</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9878,10 +9873,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125981801</v>
+        <v>125981786</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9889,21 +9884,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9913,10 +9908,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736972</v>
+        <v>737026</v>
       </c>
       <c r="R92" t="n">
-        <v>7371941</v>
+        <v>7371930</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9943,12 +9938,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Avskalad granar</t>
         </is>
       </c>
       <c r="AD92" t="b">
